--- a/pensum/ok03/OK03_Bedriftens_regnskap_Regneark_Resultat_og_balanse.xlsx
+++ b/pensum/ok03/OK03_Bedriftens_regnskap_Regneark_Resultat_og_balanse.xlsx
@@ -386,7 +386,7 @@
     <t xml:space="preserve">Avskrivninger</t>
   </si>
   <si>
-    <t xml:space="preserve">Verdifall på biler, verktøy og instrumenter. Ingen utbetaling.</t>
+    <t xml:space="preserve">Verdifall på biler, verktøy og måleinstrumenter. Ingen utbetaling.</t>
   </si>
   <si>
     <t xml:space="preserve">Andre driftskostnader</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">EGENKAPITAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Maskiner, verktøy og instrumenter</t>
+    <t xml:space="preserve">Verktøy og måleinstrumenter</t>
   </si>
   <si>
     <t xml:space="preserve">Aksjekapital</t>
@@ -1346,12 +1346,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1359,11 +1363,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1371,7 +1375,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1379,11 +1383,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1391,11 +1395,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1407,31 +1411,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1439,59 +1443,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1759,206 +1763,206 @@
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>928000</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="7" t="n">
+        <v>910650</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>620000</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="7" t="n">
+        <v>982650</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="7" t="n">
         <v>4200000</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>1400000</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="9" t="n">
         <f aca="false">B7+B8+B9</f>
-        <v>6600000</v>
-      </c>
-      <c r="C12" s="7" t="s">
+        <v>6582650</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B13" s="10" t="n">
         <f aca="false">B7/B12</f>
-        <v>0.151515151515152</v>
-      </c>
-      <c r="C13" s="7" t="s">
+        <v>0.149278785899296</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <f aca="false">B5+B6</f>
-        <v>1548000</v>
-      </c>
-      <c r="C14" s="7" t="s">
+        <v>1530650</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B16" s="12" t="n">
         <f aca="false">B8+B9</f>
         <v>5600000</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="13" t="n">
         <f aca="false">B16/B7</f>
-        <v>5.6</v>
-      </c>
-      <c r="C17" s="7" t="s">
+        <v>5.69887548974711</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="str">
+      <c r="A20" s="14" t="str">
         <f aca="false">"Bedriften tjente "&amp;TEXT(ROUND(B5,0),"#,##0")&amp;" kroner, men "&amp;TEXT(ROUND(B16,0),"#,##0")&amp;" kroner står hos kundene og på lageret. Pengene er ikke borte. De er underveis."</f>
-        <v>Bedriften tjente 928,000 kroner, men 5,600,000 kroner står hos kundene og på lageret. Pengene er ikke borte. De er underveis.</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+        <v>Bedriften tjente 910,650 kroner, men 5,600,000 kroner står hos kundene og på lageret. Pengene er ikke borte. De er underveis.</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1987,334 +1991,334 @@
   <dimension ref="A1:C54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="18" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="20" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="16" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="16" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="20" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="23" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="20" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="20" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="20" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="20" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="17" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="18" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="16" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="16" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="16" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="16" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2337,356 +2341,356 @@
   <dimension ref="A1:D36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="54"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>22400000</v>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="25" t="n">
         <f aca="false">B5/$B$5</f>
         <v>1</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>7990000</v>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">B6/$B$5</f>
         <v>0.356696428571429</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>400000</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <f aca="false">B7/$B$5</f>
         <v>0.0178571428571429</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="20" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <f aca="false">B5-B6-B7</f>
         <v>14010000</v>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="27" t="n">
         <f aca="false">B8/$B$5</f>
         <v>0.625446428571429</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>10660000</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <f aca="false">B9/$B$5</f>
         <v>0.475892857142857</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <v>620000</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <f aca="false">B10/$B$5</f>
         <v>0.0276785714285714</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>1386000</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <f aca="false">B11/$B$5</f>
         <v>0.061875</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <f aca="false">B6+B7+B9+B10+B11</f>
         <v>21056000</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <f aca="false">B12/$B$5</f>
         <v>0.94</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <f aca="false">B5-B12</f>
         <v>1344000</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <f aca="false">B13/$B$5</f>
         <v>0.06</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>56000</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <f aca="false">B14/$B$5</f>
         <v>0.0025</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="23" t="n">
-        <v>210000</v>
-      </c>
-      <c r="C15" s="24" t="n">
+      <c r="B15" s="24" t="n">
+        <v>232500</v>
+      </c>
+      <c r="C15" s="25" t="n">
         <f aca="false">B15/$B$5</f>
-        <v>0.009375</v>
-      </c>
-      <c r="D15" s="19" t="s">
+        <v>0.0103794642857143</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="26" t="n">
         <f aca="false">B13+B14-B15</f>
-        <v>1190000</v>
-      </c>
-      <c r="C16" s="26" t="n">
+        <v>1167500</v>
+      </c>
+      <c r="C16" s="27" t="n">
         <f aca="false">B16/$B$5</f>
-        <v>0.053125</v>
-      </c>
-      <c r="D16" s="19" t="s">
+        <v>0.0521205357142857</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B17" s="23" t="n">
-        <v>262000</v>
-      </c>
-      <c r="C17" s="24" t="n">
+      <c r="B17" s="24" t="n">
+        <v>256850</v>
+      </c>
+      <c r="C17" s="25" t="n">
         <f aca="false">B17/$B$5</f>
-        <v>0.0116964285714286</v>
-      </c>
-      <c r="D17" s="19" t="s">
+        <v>0.0114665178571429</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B18" s="25" t="n">
+      <c r="B18" s="26" t="n">
         <f aca="false">B16-B17</f>
-        <v>928000</v>
-      </c>
-      <c r="C18" s="26" t="n">
+        <v>910650</v>
+      </c>
+      <c r="C18" s="27" t="n">
         <f aca="false">B18/$B$5</f>
-        <v>0.0414285714285714</v>
-      </c>
-      <c r="D18" s="19" t="s">
+        <v>0.0406540178571429</v>
+      </c>
+      <c r="D18" s="20" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="29" t="n">
         <f aca="false">B13/B5</f>
         <v>0.06</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="B22" s="29" t="n">
+      <c r="B22" s="30" t="n">
         <v>0.075</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="20" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="30" t="n">
+      <c r="B23" s="31" t="n">
         <f aca="false">(B21-B22)*100</f>
         <v>-1.5</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="B24" s="26" t="n">
+      <c r="B24" s="27" t="n">
         <f aca="false">(B6+B7+B9)/B5</f>
         <v>0.850446428571429</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="20" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="31" t="str">
+      <c r="B27" s="32" t="str">
         <f aca="false">IF(ABS(B5-B12-B13)&lt;1,"OK — salgsinntekt minus sum driftskostnader er driftsresultatet","AVVIK: delsummene henger ikke sammen")</f>
         <v>OK — salgsinntekt minus sum driftskostnader er driftsresultatet</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="31" t="str">
+      <c r="B28" s="32" t="str">
         <f aca="false">IF(B21&gt;=B22,"OK — Nordlys ligger på eller over bransjens driftsmargin","AVVIK: Nordlys ligger under bransjens driftsmargin. Det er riktig med tallene som ligger inne, og det er styrets problem — ikke bankens")</f>
         <v>AVVIK: Nordlys ligger under bransjens driftsmargin. Det er riktig med tallene som ligger inne, og det er styrets problem — ikke bankens</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="16" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="17" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="B30" s="31" t="str">
+      <c r="B30" s="32" t="str">
         <f aca="false">IF(B10&gt;0,"OK — avskrivningene i B10 er en kostnad, men ingen penger gikk ut av kontoen i år. Legg dem tilbake når du vil anslå hvor mye penger driften ga","OK — ingen avskrivninger dette året")</f>
         <v>OK — avskrivningene i B10 er en kostnad, men ingen penger gikk ut av kontoen i år. Legg dem tilbake når du vil anslå hvor mye penger driften ga</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="16" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2724,362 +2728,362 @@
   <dimension ref="A1:F43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="23" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B6" s="24" t="n">
         <v>1200000</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="24" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>2400000</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="E7" s="23" t="n">
-        <v>2610000</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="E7" s="24" t="n">
+        <v>2592650</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <f aca="false">SUM(B6:B7)</f>
         <v>3600000</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">SUM(E6:E7)</f>
-        <v>2910000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
+        <v>2892650</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>1400000</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="24" t="n">
         <v>2800000</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>4200000</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">E11</f>
         <v>2800000</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="23" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D13" s="17" t="s">
+      <c r="B13" s="24" t="n">
+        <v>982650</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <f aca="false">SUM(B11:B13)</f>
-        <v>6600000</v>
-      </c>
-      <c r="D14" s="19" t="s">
+        <v>6582650</v>
+      </c>
+      <c r="D14" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <v>2100000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D15" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <v>1200000</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D16" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>890000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="19" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D17" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="24" t="n">
         <v>300000</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="21" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D18" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <f aca="false">SUM(E14:E17)</f>
         <v>4490000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B20" s="25" t="n">
+      <c r="B20" s="26" t="n">
         <f aca="false">B8+B14</f>
-        <v>10200000</v>
-      </c>
-      <c r="D20" s="17" t="s">
+        <v>10182650</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <f aca="false">E8+E12+E18</f>
-        <v>10200000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
+        <v>10182650</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <f aca="false">B20-E20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B24" s="31" t="str">
+      <c r="B24" s="32" t="str">
         <f aca="false">IF(B23=0,"OK — de to sidene er like store","AVVIK: differansen står i B23. Hver krone bedriften rår over, har kommet fra eierne eller fra noen den skylder penger")</f>
         <v>OK — de to sidene er like store</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B27" s="32" t="n">
+      <c r="B27" s="33" t="n">
         <f aca="false">E8+E12</f>
-        <v>5710000</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+        <v>5692650</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="28" t="n">
         <f aca="false">B8</f>
         <v>3600000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="B29" s="31" t="str">
+      <c r="B29" s="32" t="str">
         <f aca="false">IF(B27&gt;B28,"OK — den langsiktige finansieringen dekker anleggsmidlene, og det som er til overs finansierer en del av omløpsmidlene","AVVIK: anleggsmidlene er kortsiktig finansiert — bedriften låner kort og investerer langt")</f>
         <v>OK — den langsiktige finansieringen dekker anleggsmidlene, og det som er til overs finansierer en del av omløpsmidlene</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="28" t="n">
         <f aca="false">E18</f>
         <v>4490000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="28" t="n">
         <f aca="false">B14</f>
-        <v>6600000</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
+        <v>6582650</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="B32" s="31" t="str">
+      <c r="B32" s="32" t="str">
         <f aca="false">IF(B30&lt;B31,"OK — omløpsmidlene dekker den kortsiktige gjelden","AVVIK: den kortsiktige gjelden er større enn omløpsmidlene — bedriften er ille ute")</f>
         <v>OK — omløpsmidlene dekker den kortsiktige gjelden</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="B33" s="25" t="n">
+      <c r="B33" s="26" t="n">
         <f aca="false">B14-E18</f>
-        <v>2110000</v>
-      </c>
-      <c r="F33" s="19" t="s">
+        <v>2092650</v>
+      </c>
+      <c r="F33" s="20" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="17" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>197</v>
       </c>
-      <c r="B36" s="25" t="n">
+      <c r="B36" s="26" t="n">
         <f aca="false">B20-(E12+E18)</f>
-        <v>2910000</v>
-      </c>
-      <c r="F36" s="19" t="s">
+        <v>2892650</v>
+      </c>
+      <c r="F36" s="20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="17" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B38" s="27" t="n">
         <f aca="false">B13/B14</f>
-        <v>0.151515151515152</v>
-      </c>
-      <c r="F38" s="19" t="s">
+        <v>0.149278785899296</v>
+      </c>
+      <c r="F38" s="20" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="B39" s="32" t="n">
+      <c r="B39" s="33" t="n">
         <f aca="false">B11+B12</f>
         <v>5600000</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="19" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="B40" s="30" t="n">
+      <c r="B40" s="31" t="n">
         <f aca="false">B39/B13</f>
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
+        <v>5.69887548974711</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
         <v>204</v>
       </c>
     </row>
@@ -3117,337 +3121,337 @@
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="24" t="n">
         <v>30000</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="24" t="n">
         <v>450000</v>
       </c>
-      <c r="C9" s="33" t="n">
+      <c r="C9" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="20" t="str">
+      <c r="D9" s="21" t="str">
         <f aca="false">IF(AND(B9&gt;=$B$5,C9&gt;=$E$5),"JA — i balansen","NEI — rett i resultatet")</f>
         <v>JA — i balansen</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="28" t="n">
         <f aca="false">IF(AND(B9&gt;=$B$5,C9&gt;=$E$5),B9/C9,B9)</f>
         <v>90000</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="20" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <v>42000</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="20" t="str">
+      <c r="D10" s="21" t="str">
         <f aca="false">IF(AND(B10&gt;=$B$5,C10&gt;=$E$5),"JA — i balansen","NEI — rett i resultatet")</f>
         <v>JA — i balansen</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="28" t="n">
         <f aca="false">IF(AND(B10&gt;=$B$5,C10&gt;=$E$5),B10/C10,B10)</f>
         <v>7000</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>3500</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="20" t="str">
+      <c r="D11" s="21" t="str">
         <f aca="false">IF(AND(B11&gt;=$B$5,C11&gt;=$E$5),"JA — i balansen","NEI — rett i resultatet")</f>
         <v>NEI — rett i resultatet</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">IF(AND(B11&gt;=$B$5,C11&gt;=$E$5),B11/C11,B11)</f>
         <v>3500</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="20" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>38000</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="20" t="str">
+      <c r="D12" s="21" t="str">
         <f aca="false">IF(AND(B12&gt;=$B$5,C12&gt;=$E$5),"JA — i balansen","NEI — rett i resultatet")</f>
         <v>NEI — rett i resultatet</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">IF(AND(B12&gt;=$B$5,C12&gt;=$E$5),B12/C12,B12)</f>
         <v>38000</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
         <v>227</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <f aca="false">SUM(E9:E12)</f>
         <v>138500</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>228</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="26" t="n">
         <f aca="false">SUM(B9:B12)</f>
         <v>533500</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>229</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <f aca="false">B16-B15</f>
         <v>395000</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="B20" s="31" t="str">
+      <c r="B20" s="32" t="str">
         <f aca="false">IF(B17&gt;0,"OK — differansen i B17 ligger i balansen som anleggsmidler og kostnadsføres over flere år","OK — alt som er kjøpt, er også kostnadsført i år")</f>
         <v>OK — differansen i B17 ligger i balansen som anleggsmidler og kostnadsføres over flere år</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="B21" s="31" t="str">
+      <c r="B21" s="32" t="str">
         <f aca="false">IF(D12="NEI — rett i resultatet","OK — kabelen er montert hos kunden og brukt opp. Den er ikke et driftsmiddel, uansett hvor mye den koster","AVVIK: kabelen er ikke et driftsmiddel og skal aldri aktiveres — sett levetiden i C12 til 0")</f>
         <v>OK — kabelen er montert hos kunden og brukt opp. Den er ikke et driftsmiddel, uansett hvor mye den koster</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="23" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B25" s="28" t="n">
         <f aca="false">IF(1&lt;=$C$9,$E$9,0)</f>
         <v>90000</v>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(1,$C$9),0)</f>
         <v>360000</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="20" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="28" t="n">
         <f aca="false">IF(2&lt;=$C$9,$E$9,0)</f>
         <v>90000</v>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(2,$C$9),0)</f>
         <v>270000</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="20" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="28" t="n">
         <f aca="false">IF(3&lt;=$C$9,$E$9,0)</f>
         <v>90000</v>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(3,$C$9),0)</f>
         <v>180000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>242</v>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="28" t="n">
         <f aca="false">IF(4&lt;=$C$9,$E$9,0)</f>
         <v>90000</v>
       </c>
-      <c r="C28" s="27" t="n">
+      <c r="C28" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(4,$C$9),0)</f>
         <v>90000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="28" t="n">
         <f aca="false">IF(5&lt;=$C$9,$E$9,0)</f>
         <v>90000</v>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(5,$C$9),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="28" t="n">
         <f aca="false">IF(6&lt;=$C$9,$E$9,0)</f>
         <v>0</v>
       </c>
-      <c r="C30" s="27" t="n">
+      <c r="C30" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(6,$C$9),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="28" t="n">
         <f aca="false">IF(7&lt;=$C$9,$E$9,0)</f>
         <v>0</v>
       </c>
-      <c r="C31" s="27" t="n">
+      <c r="C31" s="28" t="n">
         <f aca="false">MAX($B$9-$E$9*MIN(7,$C$9),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
         <v>247</v>
       </c>
     </row>
@@ -3480,308 +3484,308 @@
   <dimension ref="A1:E34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="23" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="26" t="n">
         <f aca="false">Balanse!B20</f>
-        <v>10200000</v>
-      </c>
-      <c r="C6" s="19" t="s">
+        <v>10182650</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <f aca="false">Balanse!E8</f>
-        <v>2910000</v>
-      </c>
-      <c r="C7" s="19" t="s">
+        <v>2892650</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="26" t="n">
         <f aca="false">Balanse!E18</f>
         <v>4490000</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="20" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">Balanse!B14</f>
-        <v>6600000</v>
-      </c>
-      <c r="C9" s="19" t="s">
+        <v>6582650</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <f aca="false">Balanse!B11</f>
         <v>1400000</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="20" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="23" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="27" t="n">
         <f aca="false">B7/B6</f>
-        <v>0.285294117647059</v>
-      </c>
-      <c r="D14" s="29" t="n">
+        <v>0.284076345548556</v>
+      </c>
+      <c r="D14" s="30" t="n">
         <v>0.362</v>
       </c>
-      <c r="E14" s="20" t="str">
+      <c r="E14" s="21" t="str">
         <f aca="false">IF(C14&gt;=D14,"På eller over bransjen","Under bransjen")</f>
         <v>Under bransjen</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="C15" s="34" t="n">
+      <c r="C15" s="35" t="n">
         <f aca="false">(B6-B7)/B7</f>
-        <v>2.50515463917526</v>
-      </c>
-      <c r="D15" s="35" t="n">
+        <v>2.52018045736608</v>
+      </c>
+      <c r="D15" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="20" t="str">
+      <c r="E15" s="21" t="str">
         <f aca="false">IF(C15&lt;=D15,"Innenfor grensen","Over grensen")</f>
         <v>Innenfor grensen</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <f aca="false">B9/B8</f>
-        <v>1.46993318485523</v>
-      </c>
-      <c r="D16" s="29" t="n">
+        <v>1.46606904231626</v>
+      </c>
+      <c r="D16" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="20" t="str">
+      <c r="E16" s="21" t="str">
         <f aca="false">IF(C16&gt;=D16,"Over normtallet","Under normtallet")</f>
         <v>Under normtallet</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <f aca="false">(B9-B10)/B8</f>
-        <v>1.15812917594655</v>
-      </c>
-      <c r="D17" s="29" t="n">
+        <v>1.15426503340757</v>
+      </c>
+      <c r="D17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="20" t="str">
+      <c r="E17" s="21" t="str">
         <f aca="false">IF(C17&gt;=D17,"Over normtallet","Under normtallet")</f>
         <v>Over normtallet</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="B20" s="23" t="n">
+      <c r="B20" s="24" t="n">
         <v>9400000</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="28" t="n">
         <f aca="false">B6</f>
-        <v>10200000</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+        <v>10182650</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="26" t="n">
         <f aca="false">(B20+B21)/2</f>
-        <v>9800000</v>
-      </c>
-      <c r="C22" s="19" t="s">
+        <v>9791325</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="28" t="n">
         <f aca="false">B7-Resultat!B18</f>
         <v>1982000</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="20" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B24" s="28" t="n">
         <f aca="false">B7</f>
-        <v>2910000</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+        <v>2892650</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="s">
         <v>280</v>
       </c>
-      <c r="B25" s="25" t="n">
+      <c r="B25" s="26" t="n">
         <f aca="false">(B23+B24)/2</f>
-        <v>2446000</v>
-      </c>
-      <c r="C25" s="19" t="s">
+        <v>2437325</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="B28" s="31" t="str">
+      <c r="B28" s="32" t="str">
         <f aca="false">IF(AND(B6=Balanse!B20,B7=Balanse!E8,B8=Balanse!E18,B9=Balanse!B14,B10=Balanse!B11),"OK — alle fem er formler mot arket Balanse. Endrer du en post der, endrer nøkkeltallet seg her","AVVIK: en av koblingene er brutt")</f>
         <v>OK — alle fem er formler mot arket Balanse. Endrer du en post der, endrer nøkkeltallet seg her</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="B29" s="31" t="str">
+      <c r="B29" s="32" t="str">
         <f aca="false">IF(AND(C14&gt;0,C14&lt;1),"OK — egenkapitalandelen er en andel av totalkapitalen","AVVIK: egenkapitalen kan ikke være større enn totalkapitalen eller negativ")</f>
         <v>OK — egenkapitalandelen er en andel av totalkapitalen</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="B30" s="31" t="str">
+      <c r="B30" s="32" t="str">
         <f aca="false">IF(C17&lt;=C16,"OK — grad 2 er alltid lavest, fordi varelageret er trukket ut","AVVIK: varelageret kan ikke være negativt")</f>
         <v>OK — grad 2 er alltid lavest, fordi varelageret er trukket ut</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="16" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
         <v>287</v>
       </c>
     </row>
@@ -3819,345 +3823,345 @@
   <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="E4" s="33" t="n">
+      <c r="E4" s="34" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="23" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B7" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="24" t="str">
+      <c r="C7" s="25" t="str">
         <f aca="false">IF($B$7=0,"",B7/$B$7)</f>
         <v/>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B8" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="24" t="str">
+      <c r="C8" s="25" t="str">
         <f aca="false">IF($B$7=0,"",B8/$B$7)</f>
         <v/>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E8" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">B7-B8</f>
         <v>0</v>
       </c>
-      <c r="C9" s="26" t="str">
+      <c r="C9" s="27" t="str">
         <f aca="false">IF($B$7=0,"",B9/$B$7)</f>
         <v/>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="23" t="n">
+      <c r="B10" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="24" t="str">
+      <c r="C10" s="25" t="str">
         <f aca="false">IF($B$7=0,"",B10/$B$7)</f>
         <v/>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="24" t="str">
+      <c r="C11" s="25" t="str">
         <f aca="false">IF($B$7=0,"",B11/$B$7)</f>
         <v/>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">SUM(E8:E10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="23" t="n">
+      <c r="B12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="24" t="str">
+      <c r="C12" s="25" t="str">
         <f aca="false">IF($B$7=0,"",B12/$B$7)</f>
         <v/>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">E7+E11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <f aca="false">B9-B10-B11-B12</f>
         <v>0</v>
       </c>
-      <c r="C13" s="26" t="str">
+      <c r="C13" s="27" t="str">
         <f aca="false">IF($B$7=0,"",B13/$B$7)</f>
         <v/>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="B14" s="23" t="n">
+      <c r="B14" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <f aca="false">B13+B14</f>
         <v>0</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="24" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="22" t="s">
         <v>300</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="26" t="n">
         <f aca="false">E13+E14+E15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <f aca="false">B15-B16</f>
         <v>0</v>
       </c>
-      <c r="C17" s="26" t="str">
+      <c r="C17" s="27" t="str">
         <f aca="false">IF($B$7=0,"",B17/$B$7)</f>
         <v/>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <f aca="false">E12-E16</f>
         <v>0</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="20" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="B20" s="28" t="str">
+      <c r="B20" s="29" t="str">
         <f aca="false">IF($B$7=0,"",B13/$B$7)</f>
         <v/>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.075</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="B21" s="28" t="str">
+      <c r="B21" s="29" t="str">
         <f aca="false">IF($B$7=0,"",B10/$B$7)</f>
         <v/>
       </c>
-      <c r="F21" s="19" t="s">
+      <c r="F21" s="20" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B22" s="28" t="str">
+      <c r="B22" s="29" t="str">
         <f aca="false">IF(E12=0,"",E13/E12)</f>
         <v/>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.362</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="B23" s="32" t="str">
+      <c r="B23" s="33" t="str">
         <f aca="false">IF(E12=0,"",E11-E15)</f>
         <v/>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="20" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="B26" s="31" t="str">
+      <c r="B26" s="32" t="str">
         <f aca="false">IF(E12=0,"Ikke fylt ut ennå",IF(E17=0,"OK — de to sidene er like store","AVVIK: differansen står i E17 — du har glemt en post"))</f>
         <v>Ikke fylt ut ennå</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="B27" s="31" t="str">
+      <c r="B27" s="32" t="str">
         <f aca="false">IF(E12=0,"Ikke fylt ut ennå",IF(E13+E14&gt;E7,"OK — egenkapital og langsiktig gjeld dekker anleggsmidlene","AVVIK: anleggsmidlene er kortsiktig finansiert"))</f>
         <v>Ikke fylt ut ennå</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="B28" s="31" t="str">
+      <c r="B28" s="32" t="str">
         <f aca="false">IF(E12=0,"Ikke fylt ut ennå",IF(E11&gt;E15,"OK — arbeidskapitalen er positiv","AVVIK: den kortsiktige gjelden er større enn omløpsmidlene"))</f>
         <v>Ikke fylt ut ennå</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="s">
         <v>313</v>
       </c>
     </row>
@@ -4195,506 +4199,506 @@
   <dimension ref="A1:E72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="54"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="18" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="28" t="n">
         <f aca="false">Resultat!B5</f>
         <v>22400000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="28" t="n">
         <f aca="false">Balanse!B12</f>
         <v>4200000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <f aca="false">B8/B7*365</f>
         <v>68.4375</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="20" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="20" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="28" t="n">
         <f aca="false">B7*B10/365</f>
         <v>1227397.26027397</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="26" t="n">
         <f aca="false">B8-B11</f>
         <v>2972602.73972603</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="20" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="28" t="n">
         <f aca="false">Balanse!B11</f>
         <v>1400000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="B15" s="29" t="n">
+      <c r="B15" s="30" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="s">
         <v>328</v>
       </c>
-      <c r="B16" s="25" t="n">
+      <c r="B16" s="26" t="n">
         <f aca="false">B14*B15</f>
         <v>280000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="s">
         <v>329</v>
       </c>
-      <c r="B17" s="25" t="n">
+      <c r="B17" s="26" t="n">
         <f aca="false">B12+B16</f>
         <v>3252602.73972603</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="28" t="n">
         <f aca="false">Balanse!B13</f>
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+        <v>982650</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="B19" s="25" t="n">
+      <c r="B19" s="26" t="n">
         <f aca="false">B18+B17</f>
-        <v>4252602.73972603</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
+        <v>4235252.73972603</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="18" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="28" t="n">
         <f aca="false">Resultat!B18</f>
-        <v>928000</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="s">
+        <v>910650</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="28" t="n">
         <f aca="false">Resultat!B10</f>
         <v>620000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="26" t="n">
         <f aca="false">B22+B23</f>
-        <v>1548000</v>
-      </c>
-      <c r="E24" s="19" t="s">
+        <v>1530650</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="B27" s="31" t="str">
+      <c r="B27" s="32" t="str">
         <f aca="false">IF(B9&gt;B10,"AVVIK: kundene bruker lengre tid enn avtalt. Differansen er penger Nordlys låner ut gratis","OK — kundene betaler innenfor den kredittiden du sikter mot")</f>
         <v>AVVIK: kundene bruker lengre tid enn avtalt. Differansen er penger Nordlys låner ut gratis</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="16" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="B29" s="31" t="str">
+      <c r="B29" s="32" t="str">
         <f aca="false">IF(B17&gt;B18,"OK — det ligger mer penger i kundefordringer og lager enn på konto. Det er der du henter likviditet først","OK — bankinnskuddet er større enn det du kan frigjøre")</f>
         <v>OK — det ligger mer penger i kundefordringer og lager enn på konto. Det er der du henter likviditet først</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="17" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="16" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="24" t="n">
         <v>1000000</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="B36" s="23" t="n">
+      <c r="B36" s="24" t="n">
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="B37" s="33" t="n">
+      <c r="B37" s="34" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="B38" s="27" t="n">
+      <c r="B38" s="28" t="n">
         <f aca="false">Balanse!E17</f>
         <v>300000</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="19" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="B39" s="28" t="n">
+      <c r="B39" s="29" t="n">
         <f aca="false">B38/B35</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="B40" s="25" t="n">
+      <c r="B40" s="26" t="n">
         <f aca="false">B36-B35</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B43" s="26" t="n">
+      <c r="B43" s="27" t="n">
         <f aca="false">'Til kapittel 4'!C14</f>
-        <v>0.285294117647059</v>
-      </c>
-      <c r="C43" s="24" t="n">
+        <v>0.284076345548556</v>
+      </c>
+      <c r="C43" s="25" t="n">
         <f aca="false">'Til kapittel 4'!D14</f>
         <v>0.362</v>
       </c>
-      <c r="E43" s="19" t="s">
+      <c r="E43" s="20" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="19" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B44" s="26" t="n">
+      <c r="B44" s="27" t="n">
         <f aca="false">'Til kapittel 4'!C16</f>
-        <v>1.46993318485523</v>
-      </c>
-      <c r="C44" s="24" t="n">
+        <v>1.46606904231626</v>
+      </c>
+      <c r="C44" s="25" t="n">
         <f aca="false">'Til kapittel 4'!D16</f>
         <v>2</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B45" s="26" t="n">
+      <c r="B45" s="27" t="n">
         <f aca="false">'Til kapittel 4'!C17</f>
-        <v>1.15812917594655</v>
-      </c>
-      <c r="C45" s="24" t="n">
+        <v>1.15426503340757</v>
+      </c>
+      <c r="C45" s="25" t="n">
         <f aca="false">'Til kapittel 4'!D17</f>
         <v>1</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B46" s="34" t="n">
+      <c r="B46" s="35" t="n">
         <f aca="false">'Til kapittel 4'!C15</f>
-        <v>2.50515463917526</v>
-      </c>
-      <c r="C46" s="36" t="n">
+        <v>2.52018045736608</v>
+      </c>
+      <c r="C46" s="37" t="n">
         <f aca="false">'Til kapittel 4'!D15</f>
         <v>5</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="19" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="B47" s="32" t="n">
+      <c r="B47" s="33" t="n">
         <f aca="false">Balanse!B33</f>
-        <v>2110000</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
+        <v>2092650</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="18" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B50" s="30" t="n">
+      <c r="B50" s="31" t="n">
         <f aca="false">Balanse!B12/Resultat!B5*365</f>
         <v>68.4375</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="B51" s="36" t="n">
+      <c r="B51" s="37" t="n">
         <f aca="false">B50-B37</f>
         <v>48.4375</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="B52" s="25" t="n">
+      <c r="B52" s="26" t="n">
         <f aca="false">B51/365*Resultat!B5</f>
         <v>2972602.73972603</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="B53" s="30" t="n">
+      <c r="B53" s="31" t="n">
         <f aca="false">B52/B35</f>
         <v>2.97260273972603</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="E53" s="20" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="17" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="18" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="B56" s="27" t="n">
+      <c r="B56" s="28" t="n">
         <f aca="false">Resultat!B5</f>
         <v>22400000</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="19" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="20" t="s">
         <v>357</v>
       </c>
-      <c r="B57" s="23" t="n">
+      <c r="B57" s="24" t="n">
         <v>24000000</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="19" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="B58" s="32" t="n">
+      <c r="B58" s="33" t="n">
         <f aca="false">B57-B56</f>
         <v>1600000</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="19" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="B59" s="27" t="n">
+      <c r="B59" s="28" t="n">
         <f aca="false">Balanse!B12+Balanse!B11-Balanse!E14</f>
         <v>3500000</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="20" t="s">
         <v>360</v>
       </c>
-      <c r="B60" s="28" t="n">
+      <c r="B60" s="29" t="n">
         <f aca="false">B59/B56</f>
         <v>0.15625</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="21" t="s">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="B61" s="25" t="n">
+      <c r="B61" s="26" t="n">
         <f aca="false">B58*B60</f>
         <v>250000</v>
       </c>
-      <c r="E61" s="19" t="s">
+      <c r="E61" s="20" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="B62" s="28" t="n">
+      <c r="B62" s="29" t="n">
         <f aca="false">B61/B40</f>
         <v>0.25</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="17" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="18" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="19" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="20" t="s">
         <v>364</v>
       </c>
-      <c r="B65" s="31" t="str">
+      <c r="B65" s="32" t="str">
         <f aca="false">IF(B43&gt;=C43,"OK — egenkapitalandelen er på eller over bransjens nivå","AVVIK: egenkapitalandelen ligger under bransjen. Det er det første banken ser")</f>
         <v>AVVIK: egenkapitalandelen ligger under bransjen. Det er det første banken ser</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="16" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="17" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="19" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="B67" s="31" t="str">
+      <c r="B67" s="32" t="str">
         <f aca="false">IF(B45&gt;=C45,"OK — likviditetsgrad 2 er over normtallet. Det er den strengeste av de to, og den regner ikke med varelageret","AVVIK: likviditetsgrad 2 er under normtallet — bedriften kan få problemer med regningene som forfaller i år")</f>
         <v>OK — likviditetsgrad 2 er over normtallet. Det er den strengeste av de to, og den regner ikke med varelageret</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="19" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="B68" s="31" t="str">
+      <c r="B68" s="32" t="str">
         <f aca="false">IF(B38&lt;=B35,"OK — kassekreditten er trukket innenfor rammen","AVVIK: bedriften har trukket mer enn rammen tillater")</f>
         <v>OK — kassekreditten er trukket innenfor rammen</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="19" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="B69" s="31" t="str">
+      <c r="B69" s="32" t="str">
         <f aca="false">IF(B61&lt;B40,"OK — søknaden er større enn den beregnede kapitalbindingen. En ramme skal ha luft, men differansen er det første banken spør om","AVVIK: veksten binder mer kapital enn økningen det søkes om — be om mer")</f>
         <v>OK — søknaden er større enn den beregnede kapitalbindingen. En ramme skal ha luft, men differansen er det første banken spør om</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="16" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="17" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="17" t="s">
         <v>100</v>
       </c>
     </row>

--- a/pensum/ok03/OK03_Bedriftens_regnskap_Regneark_Resultat_og_balanse.xlsx
+++ b/pensum/ok03/OK03_Bedriftens_regnskap_Regneark_Resultat_og_balanse.xlsx
@@ -1346,7 +1346,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1497,6 +1497,18 @@
     </xf>
     <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1874,7 +1886,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="24.75" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>18</v>
       </c>
@@ -1887,7 +1899,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="32.25" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
@@ -2153,7 +2165,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+      <c s="38" r="A29" t="s">
         <v>66</v>
       </c>
       <c r="B29" s="20" t="s">
@@ -2179,8 +2191,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+    <row ht="27" customHeight="true" r="33" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A33" t="s">
         <v>73</v>
       </c>
       <c r="B33" s="22" t="s">
@@ -2201,8 +2213,8 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+    <row ht="27" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A35" t="s">
         <v>77</v>
       </c>
       <c r="B35" s="22" t="s">
@@ -2223,8 +2235,8 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A37" t="s">
         <v>81</v>
       </c>
       <c r="B37" s="22" t="s">
@@ -2620,8 +2632,8 @@
         <v>-1.5</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
+    <row ht="27" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A24" t="s">
         <v>141</v>
       </c>
       <c r="B24" s="27" t="n">
@@ -2646,8 +2658,8 @@
         <v>OK — salgsinntekt minus sum driftskostnader er driftsresultatet</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A28" t="s">
         <v>145</v>
       </c>
       <c r="B28" s="32" t="str">
@@ -2660,8 +2672,8 @@
         <v>146</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
+    <row ht="27" customHeight="true" r="30" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A30" t="s">
         <v>147</v>
       </c>
       <c r="B30" s="32" t="str">
@@ -3047,8 +3059,8 @@
         <v>198</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+    <row ht="27" customHeight="true" r="38" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A38" t="s">
         <v>199</v>
       </c>
       <c r="B38" s="27" t="n">
@@ -3314,8 +3326,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+    <row ht="27" customHeight="true" r="20" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A20" t="s">
         <v>231</v>
       </c>
       <c r="B20" s="32" t="str">
@@ -3337,7 +3349,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
         <v>234</v>
       </c>
@@ -3599,11 +3611,11 @@
         <v>263</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c s="38" r="B14" t="s">
         <v>265</v>
       </c>
       <c r="C14" s="27" t="n">
@@ -3618,11 +3630,11 @@
         <v>Under bransjen</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c s="38" r="B15" t="s">
         <v>267</v>
       </c>
       <c r="C15" s="35" t="n">
@@ -3637,11 +3649,11 @@
         <v>Innenfor grensen</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c s="38" r="B16" t="s">
         <v>269</v>
       </c>
       <c r="C16" s="27" t="n">
@@ -3656,11 +3668,11 @@
         <v>Under normtallet</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="39.75" customHeight="true" r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c s="38" r="B17" t="s">
         <v>271</v>
       </c>
       <c r="C17" s="27" t="n">
@@ -3747,8 +3759,8 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A28" t="s">
         <v>282</v>
       </c>
       <c r="B28" s="32" t="str">
@@ -3756,8 +3768,8 @@
         <v>OK — alle fem er formler mot arket Balanse. Endrer du en post der, endrer nøkkeltallet seg her</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+    <row ht="27" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A29" t="s">
         <v>283</v>
       </c>
       <c r="B29" s="32" t="str">
@@ -4002,8 +4014,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
+    <row ht="27" customHeight="true" r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A14" t="s">
         <v>298</v>
       </c>
       <c r="B14" s="24" t="n">
@@ -4151,8 +4163,8 @@
         <v>Ikke fylt ut ennå</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A28" t="s">
         <v>312</v>
       </c>
       <c r="B28" s="32" t="str">
@@ -4607,8 +4619,8 @@
         <v>1600000</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20" t="s">
+    <row ht="27" customHeight="true" r="59" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A59" t="s">
         <v>359</v>
       </c>
       <c r="B59" s="28" t="n">
@@ -4683,8 +4695,8 @@
         <v>OK — kassekreditten er trukket innenfor rammen</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20" t="s">
+    <row ht="27" customHeight="true" r="69" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="38" r="A69" t="s">
         <v>368</v>
       </c>
       <c r="B69" s="32" t="str">
